--- a/test-jxls/src/main/resources/t1.xlsx
+++ b/test-jxls/src/main/resources/t1.xlsx
@@ -1,17 +1,30 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -100,13 +113,13 @@
     <t>t2</t>
   </si>
   <si>
-    <t>t3</t>
+    <t>t3${var a = 0}</t>
   </si>
   <si>
-    <t>${item.t1}</t>
+    <t>${item.t1;a++}</t>
   </si>
   <si>
-    <t>${item.t2}</t>
+    <t>${a}</t>
   </si>
   <si>
     <t>${item.t3}</t>
@@ -124,16 +137,16 @@
     <t>${li.lt1}</t>
   </si>
   <si>
-    <t>${li.lt2}</t>
+    <t>${new Date().getMonth()}</t>
   </si>
   <si>
-    <t>${li.lt3}</t>
+    <t>${li.lt3.split('r')[1]}</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
   <numFmts count="4">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
@@ -853,6 +866,53 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>635</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>95885</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>286385</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>1076960</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="图片 1"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="635" y="95885"/>
+          <a:ext cx="971550" cy="981075"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1107,8 +1167,11 @@
   <sheetPr/>
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="3" outlineLevelCol="2"/>
+  <cols>
+    <col min="4" max="4" width="18.25" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" ht="102" customHeight="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1156,7 +1219,8 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
-  <legacyDrawing r:id="rId2"/>
+  <drawing r:id="rId2"/>
+  <legacyDrawing r:id="rId3"/>
 </worksheet>
 </file>
 
